--- a/StructureDefinition-heartland-patient.xlsx
+++ b/StructureDefinition-heartland-patient.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-patient</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-patient</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T15:03:58-04:00</t>
+    <t>2026-04-16T15:20:02-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -465,7 +465,7 @@
     <t>distanceToCardiology</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://heartlandprotocol.org/fhir/StructureDefinition/heartland-distance-to-cardiology}
+    <t xml:space="preserve">Extension {https://fhir.heartlandprotocol.org/StructureDefinition/heartland-distance-to-cardiology}
 </t>
   </si>
   <si>
@@ -485,7 +485,7 @@
     <t>socialSupportScore</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://heartlandprotocol.org/fhir/StructureDefinition/heartland-social-support-score}
+    <t xml:space="preserve">Extension {https://fhir.heartlandprotocol.org/StructureDefinition/heartland-social-support-score}
 </t>
   </si>
   <si>
@@ -1558,7 +1558,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.1875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="80.921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
